--- a/Streamlit Version/Hiring Folder.xlsx
+++ b/Streamlit Version/Hiring Folder.xlsx
@@ -1,15 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Roles" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Candidates" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ActivityLog" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ActivityLog" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +18,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -37,16 +42,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="FFc6efce"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E4DFEC"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -54,17 +59,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFc6c6c6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFc6c6c6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFc6c6c6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFc6c6c6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -143,10 +171,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -184,69 +212,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -270,54 +300,53 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -327,7 +356,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -336,7 +365,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -345,7 +374,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -353,10 +382,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -385,7 +414,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -398,13 +427,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
+                <a:tint val="80000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -424,101 +452,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>RoleID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>RoleName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>JDFileName</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>JDPath</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>DateCreated</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>LastUpdated</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>assistant_restaurant_manager</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Assistant Restaurant Manager</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Assistant_Restaurant_Manager_JD_2026-05-29.pdf</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>jd/Assistant_Restaurant_Manager_JD_2026-05-29.pdf</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="8" max="8"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="10" max="10"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="11" max="11"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="12" max="12"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>CandidateID</t>
@@ -580,596 +631,1719 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>assistant_restaurant_manager_91253912</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Fast Jobs</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Herman</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>91253912</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>assistant_restaurant_manager</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Assistant Restaurant Manager</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>feb 20 1988. Reasons for leaving: 5 work week to 6 days work week, wants a 5 day work week. Outlet Manager ( Last Drawn : 5.6k ) expected salary ( 4.8-5k). Used to any type of restaurants and is okay. Prepare beverages like food and wine. FHC,  Scheduling to stock order, inventory. also dealt with P&amp;L and staff management also.  had to manage wine which was very tricky.  managed 25 staff, part off the kitchen.  Notice period : 1 month.</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>Herman_91253912_Assistant_Restaurant_Manager_Herman_Yusof_Assistant_Restaurant_Manager_Fast_Food_2026-05-29.pdf</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>resumes/Herman_91253912_Assistant_Restaurant_Manager_Herman_Yusof_Assistant_Restaurant_Manager_Fast_Food_2026-05-29.pdf</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>assistant_restaurant_manager_81007322</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Fast Jobs</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Lovelyn</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>81007322</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>assistant_restaurant_manager</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Assistant Restaurant Manager</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>20/Jan/1983, Singaporean. Reasons for leaving ( signed up for an online course, planning to swtich career, but they reccommend for the work and study program but after 1-2months was not worth it, it was hard to cope. and decided to stop. currently doing part time, but want to go back to full time role. was in a managing role and sechudleing and crew training, and anything under the manageral roles. with hands on on operation roles. always training staff. have a supervisior under her to train. also do POS systems and Hiring and recuritment. has touch payroll, but also sourced to 3rd party. managed about 50 kitchen staff, in others about 30-25 staff mostly part-time. did all the loabour cost, inventory costs and restocks as well as order stocks. has managed chef and prepared food for the daily operations. has food hegeine cert. the location is okay. | area of residence ( woodlands ), expected salary 4k.</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>Lovelyn_81007322_Assistant_Restaurant_Manager_Lovelyn_ARM_2026-05-29.docx</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>resumes/Lovelyn_81007322_Assistant_Restaurant_Manager_Lovelyn_ARM_2026-05-29.docx</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_83828025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MCF</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Muhammad Imran Abdul Rahman</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>83828025</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DOB: 25/11/1980 / Singaporean.  Reasons for leaving : Toxic management, looking more positive areas. Very willing to work as ARM but also wants to progress to become a RM. Currently Salary : 4.6, Expected salary 4.3-4.4k. Notice period : 1 month notice period. managed 4 outlets by doing the sechdule and manning will be based on 15 person shuffle man all around the 4 outlets, Done kitchen as well as outside customer service. Most amount of people managed 15: Petty cash, POS as well as our cost control, leave approval, and part-timer hours all under him. usally GM report as well as resgination reports and P and L reports. halal certs, Halal, NEA/SFA, hygiene audits, workplace safety, or internal audits all have been done before.
+work arrangement : any day is okay, as long as the arrangement is in advance.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Muhammad_Imran_Abdul_Rahman_83828025_Assistant_Restaurant_Manager_Resume_2026-05-29.pdf</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>resumes/Muhammad_Imran_Abdul_Rahman_83828025_Assistant_Restaurant_Manager_Resume_2026-05-29.pdf</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_92720931</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MCF</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Yuvaraj</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>92720931</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PR but can work in singapore, Date DOB: 09/07/1987. Reasons for leaving pervious role. they are downsizing the business.  Okay with ARM.  Last Drawn Salary : 5,000 expected salary,  Negotiable.  More than 10, Kitchen and front office. at monts and terrir handing retail and front of the house. FHC up to level. Cost control, Inventory and stock take. Sluppy handing, salkes and revuyne reports and pos and petty cash. Location : Changi is okay, Area of residence : Yishun.  Quite fast paced environment in monts and terror . Notice period Immediate . Work arrangement is all 5 days, morning and night, weekends should also be okay.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yuvaraj_92720931_Assistant_Restaurant_Manager_Soundarajan_Yuvaraj_1_2026-05-29.docx</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>resumes/Yuvaraj_92720931_Assistant_Restaurant_Manager_Soundarajan_Yuvaraj_1_2026-05-29.docx</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_87177097</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Job Street</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Christopher Balanag</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>87177097</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Christopher_Balanag_87177097_Assistant_Restaurant_Manager_Christopher_Balanag_Assistant_Restaurant_Manager_Fast_Food_2026-05-29.docx</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>resumes/Christopher_Balanag_87177097_Assistant_Restaurant_Manager_Christopher_Balanag_Assistant_Restaurant_Manager_Fast_Food_2026-05-29.docx</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_84188184</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Job Street</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mohamed Fardeli Abdul Rahim</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>84188184</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Mohamed_Fardeli_Abdul_Rahim_84188184_Assistant_Restaurant_Manager_Mohamed_Fardeli_Abdul_Rahim_Assistant_Restaurant_Manager_Fast_Food_2026-05-29.rtf</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>resumes/Mohamed_Fardeli_Abdul_Rahim_84188184_Assistant_Restaurant_Manager_Mohamed_Fardeli_Abdul_Rahim_Assistant_Restaurant_Manager_Fast_Food_2026-05-29.rtf</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_81558102</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Job Street</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Noraidah mohammad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>81558102</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_90105644</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Job Street</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Winnie Lai</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>90105644</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Winnie_Lai_90105644_Assistant_Restaurant_Manager_Winnie_Lai_Assistant_Restaurant_Manager_Fast_Food_2026-05-29.pdf</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>resumes/Winnie_Lai_90105644_Assistant_Restaurant_Manager_Winnie_Lai_Assistant_Restaurant_Manager_Fast_Food_2026-05-29.pdf</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_98649955</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Job Street</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Abhishek saraf</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>98649955</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>18/8/1988, Singaporean ( LTVP Pass, Wife is PR ). Family business in Transportation business, had to take care since  it was family business, dad was not feeling well, once he's done he wanted to go back to FnB. Currently : Wild Fire join march 2025, Reasons for leaving : was looking for a restaurant manager roles ( but been asking to work as ARM. there was no career progression, looking for a better opportunity.  Currently company is a small restaurant about 60 seating, front of the house 5 people ( 4 full time + 1 part time ), ( 6 kitchen ).  Spruce is cafe based and some are Fnb and high end fine dinning and some provide services ( unclear ). in spruce had many experience.  ( managed mutiple outlets during time at spruce ). Last Drawn Salary ( 4k ), Expected Salary (4.5k). Notice period ( 1 month notice, if clear leave can start in 2 weeks ).  based on this visa dont need quota, MOC letter exprires in 2027, when submit to MOM will give NOC letter to the company, currently working in Wild Fire they will remove the NOC, Quota will not be hit. Currently applying for PR currently. Education in Computer Application but when moved to singapore focused heavily on resturant managering, did not choose to purse because his passion is in FnB Resturant Manager, but is able to do well in applying tech into audits and also reports.</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Abhishek_saraf_98649955_Assistant_Restaurant_Manager_Abhishek_saraf_Assistant_Restaurant_Manager_Fast_Food_2026-05-29.pdf</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>resumes/Abhishek_saraf_98649955_Assistant_Restaurant_Manager_Abhishek_saraf_Assistant_Restaurant_Manager_Fast_Food_2026-05-29.pdf</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>CandidateID</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Details</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2026-05-29 08:53:52</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>role created</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Assistant Restaurant Manager</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>RoleID=assistant_restaurant_manager</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2026-05-29 08:53:52</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>JD uploaded</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Assistant Restaurant Manager</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>jd/Assistant_Restaurant_Manager_JD_2026-05-29.pdf</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2026-05-29 08:54:43</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>candidate added</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Assistant Restaurant Manager</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>assistant_restaurant_manager_91253912</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Herman</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>91253912</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>New candidate</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2026-05-29 08:54:43</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>resume uploaded</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Assistant Restaurant Manager</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>assistant_restaurant_manager_91253912</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Herman</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>91253912</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>resumes/Herman_91253912_Assistant_Restaurant_Manager_Herman_Yusof_Assistant_Restaurant_Manager_Fast_Food_2026-05-29.pdf</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="18.75" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-05-29 09:01:43</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>candidate added</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Assistant Restaurant Manager</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>assistant_restaurant_manager_81007322</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Lovelyn</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>81007322</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>New candidate</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="18.75" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2026-05-29 09:01:43</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>resume uploaded</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Assistant Restaurant Manager</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>assistant_restaurant_manager_81007322</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Lovelyn</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>81007322</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>resumes/Lovelyn_81007322_Assistant_Restaurant_Manager_Lovelyn_ARM_2026-05-29.docx</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="18.75" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026-05-29 09:57:52</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>result changed</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Assistant Restaurant Manager</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>assistant_restaurant_manager_81007322</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Lovelyn</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>81007322</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Pending -&gt; Pass</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="18.75" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-05-29 09:57:53</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>candidate updated</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Assistant Restaurant Manager</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>assistant_restaurant_manager_81007322</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Lovelyn</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>81007322</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Selected candidate panel save</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="18.75" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-05-29 10:08:54</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>result changed</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Assistant Restaurant Manager</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>assistant_restaurant_manager_91253912</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Herman</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>91253912</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Pending -&gt; Called</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="18.75" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2026-05-29 10:08:54</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>candidate updated</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Assistant Restaurant Manager</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>assistant_restaurant_manager_91253912</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Herman</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>91253912</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Selected candidate panel save</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="18.75" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-05-29 10:08:59</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>result changed</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Assistant Restaurant Manager</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>assistant_restaurant_manager_91253912</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Herman</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>91253912</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Called -&gt; Pass</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13" ht="18.75" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2026-05-29 10:08:59</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>candidate updated</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Assistant Restaurant Manager</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>assistant_restaurant_manager_91253912</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Herman</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>91253912</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Selected candidate panel save</t>
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-29 14:04:05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>candidate added</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_83828025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Muhammad Imran Abdul Rahman</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>83828025</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>New candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-29 14:04:06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>resume uploaded</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_83828025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Muhammad Imran Abdul Rahman</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>83828025</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>resumes/Muhammad_Imran_Abdul_Rahman_83828025_Assistant_Restaurant_Manager_Resume_2026-05-29.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-29 14:04:38</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>candidate added</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_92720931</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Yuvaraj</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>92720931</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>New candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-29 14:04:38</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>resume uploaded</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_92720931</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Yuvaraj</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>92720931</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>resumes/Yuvaraj_92720931_Assistant_Restaurant_Manager_Soundarajan_Yuvaraj_1_2026-05-29.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-29 14:12:07</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>candidate added</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_87177097</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Christopher Balanag</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>87177097</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>New candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-29 14:12:07</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>resume uploaded</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_87177097</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Christopher Balanag</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>87177097</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>resumes/Christopher_Balanag_87177097_Assistant_Restaurant_Manager_Christopher_Balanag_Assistant_Restaurant_Manager_Fast_Food_2026-05-29.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-29 14:17:52</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>candidate added</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_84188184</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Mohamed Fardeli Abdul Rahim</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>84188184</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>New candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-29 14:17:53</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>resume uploaded</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_84188184</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mohamed Fardeli Abdul Rahim</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>84188184</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>resumes/Mohamed_Fardeli_Abdul_Rahim_84188184_Assistant_Restaurant_Manager_Mohamed_Fardeli_Abdul_Rahim_Assistant_Restaurant_Manager_Fast_Food_2026-05-29.rtf</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-29 14:18:55</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>candidate added</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_81558102</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Noraidah mohammad</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>81558102</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>New candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-29 14:21:13</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>candidate added</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_90105644</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Winnie Lai</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>90105644</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>New candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-29 14:21:14</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>resume uploaded</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_90105644</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Winnie Lai</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>90105644</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>resumes/Winnie_Lai_90105644_Assistant_Restaurant_Manager_Winnie_Lai_Assistant_Restaurant_Manager_Fast_Food_2026-05-29.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-29 14:43:49</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>candidate added</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_98649955</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Abhishek saraf</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>98649955</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>New candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-29 14:43:50</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>resume uploaded</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_98649955</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Abhishek saraf</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>98649955</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>resumes/Abhishek_saraf_98649955_Assistant_Restaurant_Manager_Winnie_Lai_Assistant_Restaurant_Manager_Fast_Food_2026-05-29.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-29 14:44:11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>resume uploaded</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_98649955</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Abhishek saraf</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>98649955</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>resumes/Abhishek_saraf_98649955_Assistant_Restaurant_Manager_Abhishek_saraf_Assistant_Restaurant_Manager_Fast_Food_2026-05-29.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-29 14:44:11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>candidate updated</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_98649955</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Abhishek saraf</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>98649955</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Updated from add form</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-29 17:05:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>candidate updated</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_92720931</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Yuvaraj</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>92720931</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Selected candidate panel save</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-29 17:12:49</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>candidate updated</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_83828025</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Muhammad Imran Abdul Rahman</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>83828025</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Selected candidate panel save</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-03 14:16:32</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>result changed</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_98649955</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Abhishek saraf</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>98649955</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pending -&gt; Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-03 14:16:32</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>candidate updated</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_98649955</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Abhishek saraf</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>98649955</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>CDD details save</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Streamlit Version/Hiring Folder.xlsx
+++ b/Streamlit Version/Hiring Folder.xlsx
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general"/>
@@ -90,6 +95,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -552,7 +558,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -1160,6 +1166,69 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_82616551</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Yugenthiri Paramanandan</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>82616551</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Contacted 15/06/2026
+Ms yugen, 15/11/1991, turning 35. Last Drawn : 3,800 ( basic ). Reasons for Leaving : the outlet is closing.  2 months notice period, expected salary, anything above 3,800. Open to work on the weekends and public holidays, is perfectly okay with an assistant manager, inorder to progress slowly and learn the ins and out.  wants to have at least 6 off days a month, 5.5 work week. Most number of people managed, 15 under ( 3 kitchen + front of the house ), she wants to manage more people, currently only running with 2 crew and wants more to manage. Bost mos burger and paris baguette had managed mutiple resturants at once due to lack of managers so managed 2 stores stimotaniously, for mos burger have been to all of it, for mos burger they only allow the outlet manager to do ordering and stock take.  have done stock take all the way to audits and checks, P&amp;L meetings, has been throught the whole specturm, from service crew, line cook then resturant manager.</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Contacted</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Yugenthiri_Paramanandan_82616551_Assistant_Restaurant_Manager_Yugenthiri_Paramanandan_Assistant_Restaurant_Manager_Fast_Food_2026-06-15.pdf</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>resumes/Yugenthiri_Paramanandan_82616551_Assistant_Restaurant_Manager_Yugenthiri_Paramanandan_Assistant_Restaurant_Manager_Fast_Food_2026-06-15.pdf</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1171,7 +1240,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -2343,6 +2412,191 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-15 10:53:18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>candidate added</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_82616551</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Yugenthiri Paramanandan</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>82616551</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>New candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-15 10:53:18</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>resume uploaded</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_82616551</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Yugenthiri Paramanandan</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>82616551</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>resumes/Yugenthiri_Paramanandan_82616551_Assistant_Restaurant_Manager_Yugenthiri_Paramanandan_Assistant_Restaurant_Manager_Fast_Food_2026-06-15.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:09:44</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>result changed</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_82616551</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Yugenthiri Paramanandan</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>82616551</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pending -&gt; Contacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:09:44</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>candidate updated</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_82616551</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Yugenthiri Paramanandan</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>82616551</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>CDD details save</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-15 17:48:25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>candidate updated</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Assistant Restaurant Manager</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>assistant_restaurant_manager_82616551</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Yugenthiri Paramanandan</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>82616551</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>CDD details save</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
